--- a/04_Маршрутные_карты/Детали/МК_PSH24-000.07.xlsx
+++ b/04_Маршрутные_карты/Детали/МК_PSH24-000.07.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Профиль сплошной 105×15, L=1260</t>
+          <t>Деталь 1260×105×15</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Профиль сплошной 105×15, L=1260</t>
+          <t>Деталь 1260×105×15</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -607,30 +607,30 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Распиловка профиля в размер L=1260 мм</t>
+          <t>Заготовка по чертежу (резка/литая/сварная заготовка), комплектование</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Ленточнопильный станок (Pilous ARG 300 / Контур-302)</t>
+          <t>Ленточнопильный станок (Pilous ARG 300 / Контур-302) / участок заготовок</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Упоры, кондуктор</t>
+          <t>По технологу</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Отклонение длины ±1 мм, торец перпендикулярен ±0,5 мм</t>
+          <t>Припуск на механическую обработку по технологу</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Контрольный замер</t>
+          <t>Входной контроль</t>
         </is>
       </c>
     </row>
@@ -642,97 +642,137 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Слесарная</t>
+          <t>Механическая</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Снятие фасок 1×45°, зачистка торцов, разметка отверстий (при наличии)</t>
+          <t>Механическая обработка по чертежу (токарно-фрезерная)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Сверлильный станок 2Н135 / сверлильно-расточной 2А135</t>
+          <t>Токарно-винторезный станок 16К20 / Doosan Puma 2600 / Фрезерный обрабатывающий центр (Haas VF-2 / 6Р13)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Свёрла, кондуктор</t>
+          <t>Универсальная оснастка</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Фаски по чертежу</t>
+          <t>Допуски по ГОСТ 25058-2016; Ra 6,3..12,5</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.1</v>
+        <v>0.71</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Визуальный</t>
+          <t>Контроль по чертежу</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Слесарная</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Снятие заусенцев, зачистка</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Заточной станок 3Б651 / зачистка УШМ</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>УШМ</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Кромки R0,5</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Визуальный</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Контрольная</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Окончательный контроль по чертежу, маркировка</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Участок ОТК: плиты поверочные, кронциркуль, УЗК-дефектоскоп</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>СИК, штампы маркировочные</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Маркировка обозначения по ГОСТ 2.316-2008</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>ОТК</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="F10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Итого норма времени на изделие (деталь), ч:</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="G11" s="3" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Нормы времени — расчётные, уточняются по нормативам предприятия.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Разраб.: отдел технической подготовки производства (ОТПП)</t>
         </is>
